--- a/single_games_predictions/raw_single_odds_during_wm.xlsx
+++ b/single_games_predictions/raw_single_odds_during_wm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\Dokumente\Institut für Sportinformatik\WM Prognose 2026\Einzelspielprognosen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\Dokumente\Institut für Sportinformatik\wc2026_predictions\single_games_predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4A3C4A-F4C5-4B9A-ACAB-1E1A6F485022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2A3E62-7895-487E-A753-7131CA9729E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Oddspedia 1X2" sheetId="1" r:id="rId1"/>
@@ -684,6 +684,69 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
+      <c r="E3">
+        <v>1.55</v>
+      </c>
+      <c r="F3">
+        <v>4.2</v>
+      </c>
+      <c r="G3">
+        <v>5.75</v>
+      </c>
+      <c r="H3">
+        <v>1.57</v>
+      </c>
+      <c r="I3">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J3">
+        <v>5.25</v>
+      </c>
+      <c r="K3">
+        <v>1.6</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>5.75</v>
+      </c>
+      <c r="N3">
+        <v>1.54</v>
+      </c>
+      <c r="O3">
+        <v>4.25</v>
+      </c>
+      <c r="P3">
+        <v>5.5</v>
+      </c>
+      <c r="Q3">
+        <v>1.57</v>
+      </c>
+      <c r="R3">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S3">
+        <v>5.25</v>
+      </c>
+      <c r="T3">
+        <v>1.5</v>
+      </c>
+      <c r="U3">
+        <v>4.5</v>
+      </c>
+      <c r="V3">
+        <v>5</v>
+      </c>
+      <c r="W3">
+        <v>1.57</v>
+      </c>
+      <c r="X3">
+        <v>4.63</v>
+      </c>
+      <c r="Y3">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">

--- a/single_games_predictions/raw_single_odds_during_wm.xlsx
+++ b/single_games_predictions/raw_single_odds_during_wm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\Dokumente\Institut für Sportinformatik\wc2026_predictions\single_games_predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2A3E62-7895-487E-A753-7131CA9729E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038F55A5-68E2-49E5-BA77-E9529EB14335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -685,28 +685,28 @@
         <v>10</v>
       </c>
       <c r="E3">
+        <v>1.5</v>
+      </c>
+      <c r="F3">
+        <v>4.33</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
         <v>1.55</v>
-      </c>
-      <c r="F3">
-        <v>4.2</v>
-      </c>
-      <c r="G3">
-        <v>5.75</v>
-      </c>
-      <c r="H3">
-        <v>1.57</v>
       </c>
       <c r="I3">
         <v>4.4000000000000004</v>
       </c>
       <c r="J3">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="K3">
         <v>1.6</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M3">
         <v>5.75</v>
@@ -715,37 +715,37 @@
         <v>1.54</v>
       </c>
       <c r="O3">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="P3">
+        <v>5.75</v>
+      </c>
+      <c r="Q3">
+        <v>1.53</v>
+      </c>
+      <c r="R3">
+        <v>4.33</v>
+      </c>
+      <c r="S3">
         <v>5.5</v>
       </c>
-      <c r="Q3">
-        <v>1.57</v>
-      </c>
-      <c r="R3">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="S3">
-        <v>5.25</v>
-      </c>
       <c r="T3">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U3">
         <v>4.5</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X3">
-        <v>4.63</v>
+        <v>4.72</v>
       </c>
       <c r="Y3">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">

--- a/single_games_predictions/raw_single_odds_during_wm.xlsx
+++ b/single_games_predictions/raw_single_odds_during_wm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\Dokumente\Institut für Sportinformatik\wc2026_predictions\single_games_predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038F55A5-68E2-49E5-BA77-E9529EB14335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C3F0E7-3FCC-448A-84CC-83C07C95AEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Oddspedia 1X2" sheetId="1" r:id="rId1"/>
@@ -761,6 +761,69 @@
       <c r="D4" t="s">
         <v>13</v>
       </c>
+      <c r="E4">
+        <v>3.6</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>1.9</v>
+      </c>
+      <c r="H4">
+        <v>3.6</v>
+      </c>
+      <c r="I4">
+        <v>3.7</v>
+      </c>
+      <c r="J4">
+        <v>1.98</v>
+      </c>
+      <c r="K4">
+        <v>3.45</v>
+      </c>
+      <c r="L4">
+        <v>3.85</v>
+      </c>
+      <c r="M4">
+        <v>1.97</v>
+      </c>
+      <c r="N4">
+        <v>3.6</v>
+      </c>
+      <c r="O4">
+        <v>3.8</v>
+      </c>
+      <c r="P4">
+        <v>1.9</v>
+      </c>
+      <c r="Q4">
+        <v>3.5</v>
+      </c>
+      <c r="R4">
+        <v>3.7</v>
+      </c>
+      <c r="S4">
+        <v>1.95</v>
+      </c>
+      <c r="T4">
+        <v>3.4</v>
+      </c>
+      <c r="U4">
+        <v>4</v>
+      </c>
+      <c r="V4">
+        <v>1.85</v>
+      </c>
+      <c r="W4">
+        <v>3.89</v>
+      </c>
+      <c r="X4">
+        <v>4.04</v>
+      </c>
+      <c r="Y4">
+        <v>1.94</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/single_games_predictions/raw_single_odds_during_wm.xlsx
+++ b/single_games_predictions/raw_single_odds_during_wm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\Dokumente\Institut für Sportinformatik\wc2026_predictions\single_games_predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C3F0E7-3FCC-448A-84CC-83C07C95AEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E60F8E-C9C5-4145-A426-153D6575F4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
   <si>
     <t>Spiel_ID</t>
   </si>
@@ -125,6 +125,42 @@
   </si>
   <si>
     <t>bf_away</t>
+  </si>
+  <si>
+    <t>deu_par</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>bet365_qualify_home</t>
+  </si>
+  <si>
+    <t>bet365_qualify_away</t>
+  </si>
+  <si>
+    <t>ub_qualify_home</t>
+  </si>
+  <si>
+    <t>ub_qualify_away</t>
+  </si>
+  <si>
+    <t>lb_qualify_home</t>
+  </si>
+  <si>
+    <t>lb_qualify_away</t>
+  </si>
+  <si>
+    <t>bw_qualify_away</t>
+  </si>
+  <si>
+    <t>bw_qualify_home</t>
+  </si>
+  <si>
+    <t>bf_qualify_home</t>
+  </si>
+  <si>
+    <t>bf_qualify_away</t>
   </si>
 </sst>
 </file>
@@ -191,12 +227,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -501,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -515,9 +555,19 @@
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="11.109375" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="26" max="26" width="21.77734375" customWidth="1"/>
+    <col min="27" max="27" width="22.5546875" customWidth="1"/>
+    <col min="28" max="28" width="19.77734375" customWidth="1"/>
+    <col min="29" max="29" width="24.77734375" customWidth="1"/>
+    <col min="30" max="30" width="17.77734375" customWidth="1"/>
+    <col min="31" max="31" width="16.109375" customWidth="1"/>
+    <col min="32" max="32" width="18" customWidth="1"/>
+    <col min="33" max="33" width="17.109375" customWidth="1"/>
+    <col min="34" max="34" width="21.77734375" customWidth="1"/>
+    <col min="35" max="35" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -593,8 +643,38 @@
       <c r="Y1" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="Z1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -671,7 +751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -748,7 +828,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -823,6 +903,113 @@
       </c>
       <c r="Y4">
         <v>1.94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46202</v>
+      </c>
+      <c r="E5">
+        <v>1.36</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>8.5</v>
+      </c>
+      <c r="H5">
+        <v>1.37</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>8.25</v>
+      </c>
+      <c r="K5">
+        <v>1.4</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>7.5</v>
+      </c>
+      <c r="N5">
+        <v>1.37</v>
+      </c>
+      <c r="O5">
+        <v>5</v>
+      </c>
+      <c r="P5">
+        <v>8.5</v>
+      </c>
+      <c r="Q5">
+        <v>1.36</v>
+      </c>
+      <c r="R5">
+        <v>4.8</v>
+      </c>
+      <c r="S5">
+        <v>8</v>
+      </c>
+      <c r="T5">
+        <v>1.36</v>
+      </c>
+      <c r="U5">
+        <v>5</v>
+      </c>
+      <c r="V5">
+        <v>7.5</v>
+      </c>
+      <c r="W5">
+        <v>1.38</v>
+      </c>
+      <c r="X5">
+        <v>5.12</v>
+      </c>
+      <c r="Y5">
+        <v>10.3</v>
+      </c>
+      <c r="Z5">
+        <v>1.17</v>
+      </c>
+      <c r="AA5">
+        <v>5</v>
+      </c>
+      <c r="AB5">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="AC5">
+        <v>4.75</v>
+      </c>
+      <c r="AD5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="AE5">
+        <v>5</v>
+      </c>
+      <c r="AF5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="AG5">
+        <v>5.25</v>
+      </c>
+      <c r="AH5">
+        <v>1.17</v>
+      </c>
+      <c r="AI5">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>

--- a/single_games_predictions/raw_single_odds_during_wm.xlsx
+++ b/single_games_predictions/raw_single_odds_during_wm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\Dokumente\Institut für Sportinformatik\wc2026_predictions\single_games_predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E60F8E-C9C5-4145-A426-153D6575F4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D61C9B-6846-4741-9244-6BF621C8D6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>Spiel_ID</t>
   </si>
@@ -161,6 +161,42 @@
   </si>
   <si>
     <t>bf_qualify_away</t>
+  </si>
+  <si>
+    <t>Frankreich</t>
+  </si>
+  <si>
+    <t>Spanien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norwegen </t>
+  </si>
+  <si>
+    <t>Argentinien</t>
+  </si>
+  <si>
+    <t>Schweiz</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Belgien</t>
+  </si>
+  <si>
+    <t>Marokko</t>
+  </si>
+  <si>
+    <t>fra_mar</t>
+  </si>
+  <si>
+    <t>spa_bel</t>
+  </si>
+  <si>
+    <t>nor_eng</t>
+  </si>
+  <si>
+    <t>arg_sch</t>
   </si>
 </sst>
 </file>
@@ -227,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -236,9 +272,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -541,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -643,34 +676,34 @@
       <c r="Y1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AF1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AG1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AH1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AI1" s="2" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1010,6 +1043,434 @@
       </c>
       <c r="AI5">
         <v>6.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46212</v>
+      </c>
+      <c r="E6">
+        <v>1.65</v>
+      </c>
+      <c r="F6">
+        <v>4.05</v>
+      </c>
+      <c r="G6">
+        <v>5.7</v>
+      </c>
+      <c r="H6">
+        <v>1.57</v>
+      </c>
+      <c r="I6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J6">
+        <v>5.75</v>
+      </c>
+      <c r="K6">
+        <v>1.6</v>
+      </c>
+      <c r="L6">
+        <v>3.8</v>
+      </c>
+      <c r="M6">
+        <v>6.25</v>
+      </c>
+      <c r="N6">
+        <v>1.6</v>
+      </c>
+      <c r="O6">
+        <v>4</v>
+      </c>
+      <c r="P6">
+        <v>5.75</v>
+      </c>
+      <c r="Q6">
+        <v>1.57</v>
+      </c>
+      <c r="R6">
+        <v>4</v>
+      </c>
+      <c r="S6">
+        <v>5.5</v>
+      </c>
+      <c r="T6">
+        <v>1.57</v>
+      </c>
+      <c r="U6">
+        <v>3.8</v>
+      </c>
+      <c r="V6">
+        <v>6</v>
+      </c>
+      <c r="W6">
+        <v>1.61</v>
+      </c>
+      <c r="X6">
+        <v>4.04</v>
+      </c>
+      <c r="Y6">
+        <v>6.88</v>
+      </c>
+      <c r="Z6">
+        <v>1.25</v>
+      </c>
+      <c r="AA6">
+        <v>4</v>
+      </c>
+      <c r="AB6">
+        <v>1.27</v>
+      </c>
+      <c r="AC6">
+        <v>3.5</v>
+      </c>
+      <c r="AD6">
+        <v>1.25</v>
+      </c>
+      <c r="AE6">
+        <v>3.5</v>
+      </c>
+      <c r="AF6">
+        <v>1.25</v>
+      </c>
+      <c r="AG6">
+        <v>3.8</v>
+      </c>
+      <c r="AH6">
+        <v>1.26</v>
+      </c>
+      <c r="AI6">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46213</v>
+      </c>
+      <c r="E7">
+        <v>1.61</v>
+      </c>
+      <c r="F7">
+        <v>3.9</v>
+      </c>
+      <c r="G7">
+        <v>5.5</v>
+      </c>
+      <c r="H7">
+        <v>1.62</v>
+      </c>
+      <c r="I7">
+        <v>3.9</v>
+      </c>
+      <c r="J7">
+        <v>5.5</v>
+      </c>
+      <c r="K7">
+        <v>1.63</v>
+      </c>
+      <c r="L7">
+        <v>3.85</v>
+      </c>
+      <c r="M7">
+        <v>5.5</v>
+      </c>
+      <c r="N7">
+        <v>1.62</v>
+      </c>
+      <c r="O7">
+        <v>4</v>
+      </c>
+      <c r="P7">
+        <v>5.5</v>
+      </c>
+      <c r="Q7">
+        <v>1.61</v>
+      </c>
+      <c r="R7">
+        <v>3.9</v>
+      </c>
+      <c r="S7">
+        <v>5.5</v>
+      </c>
+      <c r="T7">
+        <v>1.61</v>
+      </c>
+      <c r="U7">
+        <v>3.8</v>
+      </c>
+      <c r="V7">
+        <v>5.25</v>
+      </c>
+      <c r="W7">
+        <v>1.66</v>
+      </c>
+      <c r="X7">
+        <v>4.04</v>
+      </c>
+      <c r="Y7">
+        <v>5.9</v>
+      </c>
+      <c r="Z7">
+        <v>1.3</v>
+      </c>
+      <c r="AA7">
+        <v>3.5</v>
+      </c>
+      <c r="AB7">
+        <v>1.29</v>
+      </c>
+      <c r="AC7">
+        <v>3.3</v>
+      </c>
+      <c r="AD7">
+        <v>1.28</v>
+      </c>
+      <c r="AE7">
+        <v>3.4</v>
+      </c>
+      <c r="AF7">
+        <v>1.29</v>
+      </c>
+      <c r="AG7">
+        <v>3.4</v>
+      </c>
+      <c r="AH7">
+        <v>1.34</v>
+      </c>
+      <c r="AI7">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46214</v>
+      </c>
+      <c r="E8">
+        <v>4.2</v>
+      </c>
+      <c r="F8">
+        <v>3.7</v>
+      </c>
+      <c r="G8">
+        <v>1.85</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>3.75</v>
+      </c>
+      <c r="J8">
+        <v>1.85</v>
+      </c>
+      <c r="K8">
+        <v>4</v>
+      </c>
+      <c r="L8">
+        <v>3.75</v>
+      </c>
+      <c r="M8">
+        <v>1.9</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8">
+        <v>3.75</v>
+      </c>
+      <c r="P8">
+        <v>1.9</v>
+      </c>
+      <c r="Q8">
+        <v>4</v>
+      </c>
+      <c r="R8">
+        <v>3.7</v>
+      </c>
+      <c r="S8">
+        <v>1.83</v>
+      </c>
+      <c r="T8">
+        <v>4</v>
+      </c>
+      <c r="U8">
+        <v>3.6</v>
+      </c>
+      <c r="V8">
+        <v>1.91</v>
+      </c>
+      <c r="W8">
+        <v>4.43</v>
+      </c>
+      <c r="X8">
+        <v>3.79</v>
+      </c>
+      <c r="Y8">
+        <v>1.9</v>
+      </c>
+      <c r="Z8">
+        <v>2.75</v>
+      </c>
+      <c r="AA8">
+        <v>1.44</v>
+      </c>
+      <c r="AB8">
+        <v>2.65</v>
+      </c>
+      <c r="AC8">
+        <v>1.42</v>
+      </c>
+      <c r="AD8">
+        <v>2.62</v>
+      </c>
+      <c r="AE8">
+        <v>1.44</v>
+      </c>
+      <c r="AF8">
+        <v>2.75</v>
+      </c>
+      <c r="AG8">
+        <v>1.4</v>
+      </c>
+      <c r="AH8">
+        <v>2.9</v>
+      </c>
+      <c r="AI8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46215</v>
+      </c>
+      <c r="E9">
+        <v>1.7</v>
+      </c>
+      <c r="F9">
+        <v>3.5</v>
+      </c>
+      <c r="G9">
+        <v>5.5</v>
+      </c>
+      <c r="H9">
+        <v>1.73</v>
+      </c>
+      <c r="I9">
+        <v>3.5</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <v>1.73</v>
+      </c>
+      <c r="L9">
+        <v>3.5</v>
+      </c>
+      <c r="M9">
+        <v>5.5</v>
+      </c>
+      <c r="N9">
+        <v>1.73</v>
+      </c>
+      <c r="O9">
+        <v>3.6</v>
+      </c>
+      <c r="P9">
+        <v>5.25</v>
+      </c>
+      <c r="Q9">
+        <v>1.73</v>
+      </c>
+      <c r="R9">
+        <v>3.5</v>
+      </c>
+      <c r="S9">
+        <v>5</v>
+      </c>
+      <c r="T9">
+        <v>1.7</v>
+      </c>
+      <c r="U9">
+        <v>3.5</v>
+      </c>
+      <c r="V9">
+        <v>5</v>
+      </c>
+      <c r="W9">
+        <v>1.74</v>
+      </c>
+      <c r="X9">
+        <v>3.65</v>
+      </c>
+      <c r="Y9">
+        <v>5.9</v>
+      </c>
+      <c r="Z9">
+        <v>1.33</v>
+      </c>
+      <c r="AA9">
+        <v>3.4</v>
+      </c>
+      <c r="AB9">
+        <v>1.33</v>
+      </c>
+      <c r="AC9">
+        <v>3.1</v>
+      </c>
+      <c r="AD9">
+        <v>1.33</v>
+      </c>
+      <c r="AE9">
+        <v>3.1</v>
+      </c>
+      <c r="AF9">
+        <v>1.3</v>
+      </c>
+      <c r="AG9">
+        <v>3.3</v>
+      </c>
+      <c r="AH9">
+        <v>1.36</v>
+      </c>
+      <c r="AI9">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/single_games_predictions/raw_single_odds_during_wm.xlsx
+++ b/single_games_predictions/raw_single_odds_during_wm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\Dokumente\Institut für Sportinformatik\wc2026_predictions\single_games_predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D61C9B-6846-4741-9244-6BF621C8D6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{170F02C0-AD90-4372-9112-BEE273AD7E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
   <si>
     <t>Spiel_ID</t>
   </si>
@@ -197,6 +197,12 @@
   </si>
   <si>
     <t>arg_sch</t>
+  </si>
+  <si>
+    <t>fra_spa</t>
+  </si>
+  <si>
+    <t>eng_arg</t>
   </si>
 </sst>
 </file>
@@ -574,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1473,6 +1479,220 @@
         <v>3.5</v>
       </c>
     </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46217</v>
+      </c>
+      <c r="E10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F10">
+        <v>3.25</v>
+      </c>
+      <c r="G10">
+        <v>3.25</v>
+      </c>
+      <c r="H10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I10">
+        <v>3.1</v>
+      </c>
+      <c r="J10">
+        <v>3.25</v>
+      </c>
+      <c r="K10">
+        <v>2.4</v>
+      </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
+      <c r="M10">
+        <v>3.25</v>
+      </c>
+      <c r="N10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="O10">
+        <v>3.3</v>
+      </c>
+      <c r="P10">
+        <v>3.3</v>
+      </c>
+      <c r="Q10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="R10">
+        <v>3.1</v>
+      </c>
+      <c r="S10">
+        <v>3.3</v>
+      </c>
+      <c r="T10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="U10">
+        <v>3.1</v>
+      </c>
+      <c r="V10">
+        <v>3.2</v>
+      </c>
+      <c r="W10">
+        <v>2.39</v>
+      </c>
+      <c r="X10">
+        <v>3.25</v>
+      </c>
+      <c r="Y10">
+        <v>3.35</v>
+      </c>
+      <c r="Z10">
+        <v>1.62</v>
+      </c>
+      <c r="AA10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AB10">
+        <v>1.65</v>
+      </c>
+      <c r="AC10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AD10">
+        <v>1.65</v>
+      </c>
+      <c r="AE10">
+        <v>2.15</v>
+      </c>
+      <c r="AF10">
+        <v>1.65</v>
+      </c>
+      <c r="AG10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AH10">
+        <v>1.67</v>
+      </c>
+      <c r="AI10">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46218</v>
+      </c>
+      <c r="E11">
+        <v>2.63</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>2.6</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>2.95</v>
+      </c>
+      <c r="K11">
+        <v>2.6</v>
+      </c>
+      <c r="L11">
+        <v>2.9</v>
+      </c>
+      <c r="M11">
+        <v>3.05</v>
+      </c>
+      <c r="N11">
+        <v>2.6</v>
+      </c>
+      <c r="O11">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>3</v>
+      </c>
+      <c r="Q11">
+        <v>2.6</v>
+      </c>
+      <c r="R11">
+        <v>3</v>
+      </c>
+      <c r="S11">
+        <v>2.9</v>
+      </c>
+      <c r="T11">
+        <v>2.6</v>
+      </c>
+      <c r="U11">
+        <v>2.9</v>
+      </c>
+      <c r="V11">
+        <v>2.9</v>
+      </c>
+      <c r="W11">
+        <v>2.72</v>
+      </c>
+      <c r="X11">
+        <v>3.01</v>
+      </c>
+      <c r="Y11">
+        <v>3.11</v>
+      </c>
+      <c r="Z11">
+        <v>1.73</v>
+      </c>
+      <c r="AA11">
+        <v>2.1</v>
+      </c>
+      <c r="AB11">
+        <v>1.78</v>
+      </c>
+      <c r="AC11">
+        <v>2</v>
+      </c>
+      <c r="AD11">
+        <v>1.75</v>
+      </c>
+      <c r="AE11">
+        <v>1.95</v>
+      </c>
+      <c r="AF11">
+        <v>1.8</v>
+      </c>
+      <c r="AG11">
+        <v>1.95</v>
+      </c>
+      <c r="AH11">
+        <v>1.79</v>
+      </c>
+      <c r="AI11">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/single_games_predictions/raw_single_odds_during_wm.xlsx
+++ b/single_games_predictions/raw_single_odds_during_wm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Documents\Dokumente\Institut für Sportinformatik\wc2026_predictions\single_games_predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{170F02C0-AD90-4372-9112-BEE273AD7E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58501ABA-CBDA-478C-8E86-E82474B5689D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
   <si>
     <t>Spiel_ID</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>eng_arg</t>
+  </si>
+  <si>
+    <t>fra_eng</t>
+  </si>
+  <si>
+    <t>spa_arg</t>
   </si>
 </sst>
 </file>
@@ -580,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1693,6 +1699,160 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="3">
+        <v>46221</v>
+      </c>
+      <c r="E12">
+        <v>1.91</v>
+      </c>
+      <c r="F12">
+        <v>3.8</v>
+      </c>
+      <c r="G12">
+        <v>3.8</v>
+      </c>
+      <c r="H12">
+        <v>1.93</v>
+      </c>
+      <c r="I12">
+        <v>3.75</v>
+      </c>
+      <c r="J12">
+        <v>3.7</v>
+      </c>
+      <c r="K12">
+        <v>1.9</v>
+      </c>
+      <c r="L12">
+        <v>3.7</v>
+      </c>
+      <c r="M12">
+        <v>3.85</v>
+      </c>
+      <c r="N12">
+        <v>1.91</v>
+      </c>
+      <c r="O12">
+        <v>3.8</v>
+      </c>
+      <c r="P12">
+        <v>3.8</v>
+      </c>
+      <c r="Q12">
+        <v>1.91</v>
+      </c>
+      <c r="R12">
+        <v>3.7</v>
+      </c>
+      <c r="S12">
+        <v>3.7</v>
+      </c>
+      <c r="T12">
+        <v>1.85</v>
+      </c>
+      <c r="U12">
+        <v>3.8</v>
+      </c>
+      <c r="V12">
+        <v>3.8</v>
+      </c>
+      <c r="W12">
+        <v>1.95</v>
+      </c>
+      <c r="X12">
+        <v>3.94</v>
+      </c>
+      <c r="Y12">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="3">
+        <v>46222</v>
+      </c>
+      <c r="E13">
+        <v>2.25</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>3.5</v>
+      </c>
+      <c r="H13">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>3.5</v>
+      </c>
+      <c r="K13">
+        <v>2.4</v>
+      </c>
+      <c r="L13">
+        <v>2.95</v>
+      </c>
+      <c r="M13">
+        <v>3.4</v>
+      </c>
+      <c r="N13">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="O13">
+        <v>3.1</v>
+      </c>
+      <c r="P13">
+        <v>3.5</v>
+      </c>
+      <c r="Q13">
+        <v>2.25</v>
+      </c>
+      <c r="R13">
+        <v>3</v>
+      </c>
+      <c r="S13">
+        <v>3.4</v>
+      </c>
+      <c r="T13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="U13">
+        <v>2.9</v>
+      </c>
+      <c r="V13">
+        <v>3.5</v>
+      </c>
+      <c r="W13">
+        <v>2.35</v>
+      </c>
+      <c r="X13">
+        <v>3.06</v>
+      </c>
+      <c r="Y13">
+        <v>3.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
